--- a/artfynd/S 5067-2024 artfynd.xlsx
+++ b/artfynd/S 5067-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>127163140</v>
       </c>
       <c r="B5" t="n">
-        <v>43274</v>
+        <v>43279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 5067-2024 artfynd.xlsx
+++ b/artfynd/S 5067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678259</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999476</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17246574</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127163140</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124602</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767282</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60502185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,8 +1600,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107251231</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 5067-2024 artfynd.xlsx
+++ b/artfynd/S 5067-2024 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>127163140</v>
       </c>
       <c r="B5" t="n">
-        <v>43279</v>
+        <v>43284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 5067-2024 artfynd.xlsx
+++ b/artfynd/S 5067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56124602</v>
+        <v>127163140</v>
       </c>
       <c r="B5" t="n">
-        <v>107708</v>
+        <v>43284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,43 +1041,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>100399</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Turkos blåvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Aricia nicias</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Meigen, 1829)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västanåskogen i söder, Upl</t>
+          <t>Mohällsvägen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630026</v>
+        <v>628773</v>
       </c>
       <c r="R5" t="n">
-        <v>6715912</v>
+        <v>6717273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,17 +1112,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-07-30</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-07-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>fd avlastplats</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,30 +1126,31 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Göran Frisk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Göran Frisk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56124602</t>
+          <t>https://artportalen.se/Sighting/127163140</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88767282</v>
+        <v>56124602</v>
       </c>
       <c r="B6" t="n">
         <v>107708</v>
@@ -1176,7 +1180,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,14 +1190,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>skogsväg, Västanåskogen, Upl</t>
+          <t>Västanåskogen i söder, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630041</v>
+        <v>630026</v>
       </c>
       <c r="R6" t="n">
-        <v>6715916</v>
+        <v>6715912</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,12 +1224,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2014-07-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2014-07-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>fd avlastplats</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,50 +1260,63 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88767282</t>
+          <t>https://artportalen.se/Sighting/56124602</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60502185</v>
+        <v>88767282</v>
       </c>
       <c r="B7" t="n">
-        <v>97977</v>
+        <v>107708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221944</v>
+        <v>245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västermurarna N-ut, Upl</t>
+          <t>skogsväg, Västanåskogen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629636</v>
+        <v>630041</v>
       </c>
       <c r="R7" t="n">
-        <v>6713512</v>
+        <v>6715916</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,22 +1340,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,36 +1356,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Röjd ungskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Sebastian Sundberg, Jan Edelsjö, Peter Ståhl, Tommy Löfgren</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60502185</t>
+          <t>https://artportalen.se/Sighting/88767282</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107251231</v>
+        <v>60502185</v>
       </c>
       <c r="B8" t="n">
-        <v>58327</v>
+        <v>97977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,43 +1388,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221944</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Per-Nilsmyren, Upl</t>
+          <t>Västermurarna N-ut, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626712</v>
+        <v>629636</v>
       </c>
       <c r="R8" t="n">
-        <v>6707260</v>
+        <v>6713512</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,22 +1438,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-12</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-12</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,20 +1464,143 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Röjd ungskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Lindell</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Lindell</t>
+          <t>Joakim Ekman, Sebastian Sundberg, Jan Edelsjö, Peter Ståhl, Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60502185</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>107251231</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Per-Nilsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626712</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6707260</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-03-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-03-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Lindell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Lindell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107251231</t>
         </is>
@@ -1495,6 +1615,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 5067-2024 artfynd.xlsx
+++ b/artfynd/S 5067-2024 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>127163140</v>
       </c>
       <c r="B5" t="n">
-        <v>43284</v>
+        <v>43286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
